--- a/doctool/test/auto/scenario23/システム機能設計書_サンプル_S23_レビュー記録票_expected.xlsx
+++ b/doctool/test/auto/scenario23/システム機能設計書_サンプル_S23_レビュー記録票_expected.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr filterPrivacy="1" updateLinks="never" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E173D46-3B94-4028-85F8-118B4415BB21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69B4D97A-485E-4B65-A4C1-67ED6706C574}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1381,7 +1381,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="206">
   <si>
     <t>レビュー対象物</t>
     <rPh sb="4" eb="7">
@@ -2611,9 +2611,6 @@
 </t>
   </si>
   <si>
-    <t>鈴木　花子</t>
-  </si>
-  <si>
     <t>02_要件誤り</t>
   </si>
   <si>
@@ -2646,6 +2643,9 @@
   </si>
   <si>
     <t>詳細設計</t>
+  </si>
+  <si>
+    <t>取得できませんでした</t>
   </si>
 </sst>
 </file>
@@ -4743,7 +4743,7 @@
       </c>
       <c r="B1" s="77"/>
       <c r="C1" s="90" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D1" s="91"/>
       <c r="E1" s="100" t="s">
@@ -5179,7 +5179,7 @@
       <c r="I15" s="15"/>
       <c r="J15" s="15"/>
       <c r="K15" s="19" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="L15" s="15"/>
       <c r="M15" s="15"/>
@@ -5485,9 +5485,7 @@
       </c>
       <c r="K5" s="26"/>
       <c r="L5" s="28"/>
-      <c r="M5" s="28" t="s">
-        <v>197</v>
-      </c>
+      <c r="M5" s="28"/>
       <c r="N5" s="30"/>
       <c r="O5" s="31"/>
     </row>
@@ -5500,26 +5498,24 @@
         <v>1</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
       <c r="F6" s="26"/>
       <c r="G6" s="26"/>
       <c r="H6" s="27" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I6" s="28" t="s">
         <v>193</v>
       </c>
       <c r="J6" s="27" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="K6" s="26"/>
       <c r="L6" s="28"/>
-      <c r="M6" s="28" t="s">
-        <v>197</v>
-      </c>
+      <c r="M6" s="28"/>
       <c r="N6" s="30"/>
       <c r="O6" s="31"/>
     </row>
@@ -5532,29 +5528,27 @@
         <v>1</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D7" s="26"/>
       <c r="E7" s="26"/>
       <c r="F7" s="26"/>
       <c r="G7" s="26"/>
       <c r="H7" s="27" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I7" s="28" t="s">
         <v>193</v>
       </c>
       <c r="J7" s="27" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="K7" s="26"/>
       <c r="L7" s="28"/>
-      <c r="M7" s="28" t="s">
-        <v>197</v>
-      </c>
+      <c r="M7" s="28"/>
       <c r="N7" s="30"/>
       <c r="O7" s="31" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="60" customHeight="1">
